--- a/EXP_2/READINGS/CC_OUTPUT.xlsx
+++ b/EXP_2/READINGS/CC_OUTPUT.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EDC_LAB\EXP_2\READINGS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF394097-637F-4F39-BD8A-C9304BF7D599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1724D20E-A61D-4AA9-BFAB-E86DCEAB0689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BCD9162F-5F87-46DD-B2B0-2AB68951FA17}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{08DD0450-2F20-4520-B806-FF4A691A3BFD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Output" sheetId="1" r:id="rId1"/>
+    <sheet name="Input" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,18 +37,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>VEC</t>
+    <t>VBC</t>
   </si>
   <si>
-    <t>IB(uA)(IB=20u)</t>
+    <t>IEmA(IB=20u)</t>
   </si>
   <si>
-    <t>IB(uA)(IB=60u)</t>
+    <t>IEmA(IB=60u)</t>
   </si>
   <si>
-    <t>IB(uA)(IB=100u)</t>
+    <t>VCE</t>
+  </si>
+  <si>
+    <t>IEmA(IB=90u)</t>
+  </si>
+  <si>
+    <t>IBuA(VCE=1v)</t>
+  </si>
+  <si>
+    <t>IBuA(VCE=5v)</t>
+  </si>
+  <si>
+    <t>IBuA(VCE=10v)</t>
   </si>
 </sst>
 </file>
@@ -56,7 +71,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -100,6 +115,2810 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>IEmA(IB=20u)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Output!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Output!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.33</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.46</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.59</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F276-4CE5-82D4-7B2CDA7F567C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1170106271"/>
+        <c:axId val="1163453135"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1170106271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1163453135"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1163453135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1170106271"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>IEmA(IB=60u)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Output!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Output!$C$2:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.97</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.190000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.57</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18.850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19.649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.05</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9B88-4851-9721-4DB4CB876D14}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="956571807"/>
+        <c:axId val="957287087"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="956571807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="957287087"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="957287087"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="956571807"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Output!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>IEmA(IB=90u)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Output!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Output!$D$2:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.07</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24.62</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27.22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>28.88</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31.85</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C373-4B8A-A0B5-DF6326CC5DD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1048793343"/>
+        <c:axId val="550057807"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1048793343"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="550057807"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="550057807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1048793343"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2381</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>40481</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{784BE76D-8658-ABA8-38DF-E65DA731BA46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>159543</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>197643</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A403BF3A-192B-10C9-8921-3B63B4CC8AFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>92868</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>130968</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF1E79F9-39BD-8A3D-9A11-770ECDCACE95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -111,39 +2930,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -195,7 +3014,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -306,13 +3125,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -321,6 +3133,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -385,24 +3204,44 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5EA6D88-4E10-47A8-B9CD-E65A8E9A1ECC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC573FFC-BC4D-43F4-AADC-6855C1EDCDD2}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -411,7 +3250,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -419,13 +3258,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -433,13 +3272,13 @@
         <v>0.5</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>6.2</v>
       </c>
       <c r="C3">
-        <v>225.8</v>
+        <v>15.97</v>
       </c>
       <c r="D3">
-        <v>423.7</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -447,13 +3286,13 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>62.2</v>
+        <v>6.25</v>
       </c>
       <c r="C4">
-        <v>233.7</v>
+        <v>18.190000000000001</v>
       </c>
       <c r="D4">
-        <v>437.8</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -461,13 +3300,13 @@
         <v>1.5</v>
       </c>
       <c r="B5">
-        <v>64.3</v>
+        <v>6.3</v>
       </c>
       <c r="C5">
-        <v>241</v>
+        <v>18.57</v>
       </c>
       <c r="D5">
-        <v>450.6</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -475,13 +3314,13 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>66.2</v>
+        <v>6.33</v>
       </c>
       <c r="C6">
-        <v>247.9</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="D6">
-        <v>462.6</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -489,13 +3328,13 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>74.2</v>
+        <v>6.46</v>
       </c>
       <c r="C7">
-        <v>275.7</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="D7">
-        <v>512</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -503,13 +3342,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>86.8</v>
+        <v>6.59</v>
       </c>
       <c r="C8">
-        <v>328.2</v>
+        <v>21.05</v>
       </c>
       <c r="D8">
-        <v>615.20000000000005</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -517,13 +3356,173 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>126.9</v>
+        <v>6.74</v>
       </c>
       <c r="C9">
-        <v>581</v>
+        <v>21.9</v>
       </c>
       <c r="D9">
-        <v>1258</v>
+        <v>31.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76118884-E6DE-4FFA-BEE6-2251B25889A8}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>-1.94</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>-1.5</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>-1.9</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>-1.45</v>
+      </c>
+      <c r="B5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>-1.41</v>
+      </c>
+      <c r="B6">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>-1.35</v>
+      </c>
+      <c r="B7">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>-1.3</v>
+      </c>
+      <c r="B8">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>-1.31</v>
+      </c>
+      <c r="B9">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>-1.3</v>
+      </c>
+      <c r="B10">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>-1.29</v>
+      </c>
+      <c r="B11">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
